--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="516">
   <si>
     <t>Filename</t>
   </si>
@@ -808,763 +808,760 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.4225,0.4097,0.0498,0.0077</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.2741,0.0012,0.0035,0.7856</t>
-  </si>
-  <si>
-    <t>0.0299,0.0006,0.0021,0.9847</t>
-  </si>
-  <si>
-    <t>0.9725,0.0089,0.0088,0.0007</t>
-  </si>
-  <si>
-    <t>0.9442,0.0463,0.0095,0.0022</t>
-  </si>
-  <si>
-    <t>0.9552,0.0410,0.0053,0.0011</t>
-  </si>
-  <si>
-    <t>0.9717,0.0159,0.0060,0.0020</t>
-  </si>
-  <si>
-    <t>0.9507,0.0364,0.0102,0.0023</t>
-  </si>
-  <si>
-    <t>0.9123,0.0753,0.0113,0.0024</t>
-  </si>
-  <si>
-    <t>0.9598,0.0245,0.0082,0.0021</t>
-  </si>
-  <si>
-    <t>0.9701,0.0150,0.0069,0.0014</t>
-  </si>
-  <si>
-    <t>0.8722,0.0030,0.1239,0.0004</t>
-  </si>
-  <si>
-    <t>0.0079,0.0082,0.9845,0.0009</t>
-  </si>
-  <si>
-    <t>0.0580,0.0033,0.9413,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0006,0.9980,0.0006</t>
-  </si>
-  <si>
-    <t>0.1039,0.0057,0.8888,0.0035</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0000</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9278,0.0162,0.0139,0.0023</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9621,0.0008,0.0025,0.0111</t>
+  </si>
+  <si>
+    <t>0.0029,0.0004,0.0002,0.9990</t>
+  </si>
+  <si>
+    <t>0.8468,0.0412,0.0600,0.0017</t>
+  </si>
+  <si>
+    <t>0.9278,0.0448,0.0174,0.0020</t>
+  </si>
+  <si>
+    <t>0.9474,0.0385,0.0092,0.0016</t>
+  </si>
+  <si>
+    <t>0.9622,0.0221,0.0086,0.0021</t>
+  </si>
+  <si>
+    <t>0.8451,0.1425,0.0202,0.0024</t>
+  </si>
+  <si>
+    <t>0.8760,0.1104,0.0162,0.0024</t>
+  </si>
+  <si>
+    <t>0.9545,0.0356,0.0073,0.0022</t>
+  </si>
+  <si>
+    <t>0.9883,0.0041,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.7316,0.0082,0.2570,0.0003</t>
+  </si>
+  <si>
+    <t>0.0135,0.0037,0.9802,0.0007</t>
+  </si>
+  <si>
+    <t>0.0869,0.0455,0.8480,0.0007</t>
+  </si>
+  <si>
+    <t>0.0114,0.0077,0.9741,0.0061</t>
+  </si>
+  <si>
+    <t>0.5572,0.0149,0.4139,0.0024</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0015,0.9961,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1053,0.0033,0.8734,0.0084</t>
-  </si>
-  <si>
-    <t>0.0089,0.0107,0.9790,0.0020</t>
-  </si>
-  <si>
-    <t>0.0060,0.0002,0.9929,0.0004</t>
-  </si>
-  <si>
-    <t>0.0028,0.0011,0.9958,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0020,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0000</t>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.9913,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1417,0.0302,0.7242,0.0119</t>
+  </si>
+  <si>
+    <t>0.2755,0.0049,0.6756,0.0091</t>
+  </si>
+  <si>
+    <t>0.0019,0.0013,0.9958,0.0007</t>
+  </si>
+  <si>
+    <t>0.0052,0.0010,0.9915,0.0005</t>
+  </si>
+  <si>
+    <t>0.0035,0.0007,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9995,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0275,0.9625,0.0056,0.0015</t>
-  </si>
-  <si>
-    <t>0.0591,0.0466,0.8818,0.0020</t>
+    <t>0.1789,0.8313,0.0096,0.0007</t>
+  </si>
+  <si>
+    <t>0.2145,0.0483,0.7147,0.0023</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9557,0.4810,0.0002</t>
+  </si>
+  <si>
+    <t>0.9613,0.0214,0.0040,0.0009</t>
+  </si>
+  <si>
+    <t>0.4230,0.0168,0.4743,0.0018</t>
+  </si>
+  <si>
+    <t>0.0345,0.9470,0.0194,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9914,0.0108,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.6233,0.9905,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0023,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0176,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0071,0.0007,0.9899,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.5904,0.9707,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.0156,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.4669,0.0015,0.9515</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0074,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.3632,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6064,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0056,0.0039,0.9869,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0030,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.6992,0.2432,0.0376,0.0032</t>
+  </si>
+  <si>
+    <t>0.9240,0.0079,0.0305,0.0029</t>
+  </si>
+  <si>
+    <t>0.8230,0.0605,0.0598,0.0035</t>
+  </si>
+  <si>
+    <t>0.0000,0.0331,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9689,0.0121,0.0077,0.0012</t>
+  </si>
+  <si>
+    <t>0.9673,0.0335,0.0034,0.0009</t>
+  </si>
+  <si>
+    <t>0.4028,0.5849,0.0234,0.0035</t>
+  </si>
+  <si>
+    <t>0.0000,0.9932,0.9844,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0103,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0079,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9943,0.9872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9979,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.2002,0.0086,0.8156,0.0009</t>
+  </si>
+  <si>
+    <t>0.0601,0.0091,0.9252,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0350,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9933,0.8438,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9817,0.9530,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.2155,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9948,0.9394,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.2663,0.9557</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0007,0.9996</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0272,0.9968</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0069,0.9985</t>
+  </si>
+  <si>
+    <t>0.0001,0.9936,0.7441,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9917,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9950,0.9659,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9937,0.4668,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9767,0.9865,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9560,0.0000</t>
+  </si>
+  <si>
+    <t>0.8706,0.1289,0.0117,0.0021</t>
+  </si>
+  <si>
+    <t>0.8784,0.0803,0.0286,0.0019</t>
+  </si>
+  <si>
+    <t>0.3493,0.6961,0.0066,0.0012</t>
+  </si>
+  <si>
+    <t>0.7335,0.2967,0.0090,0.0016</t>
+  </si>
+  <si>
+    <t>0.6507,0.3444,0.0195,0.0029</t>
+  </si>
+  <si>
+    <t>0.4341,0.3247,0.1332,0.0012</t>
+  </si>
+  <si>
+    <t>0.8874,0.0484,0.0351,0.0034</t>
+  </si>
+  <si>
+    <t>0.7838,0.2033,0.0225,0.0009</t>
+  </si>
+  <si>
+    <t>0.9699,0.0167,0.0063,0.0027</t>
+  </si>
+  <si>
+    <t>0.7906,0.1607,0.0335,0.0020</t>
+  </si>
+  <si>
+    <t>0.9765,0.0126,0.0038,0.0024</t>
+  </si>
+  <si>
+    <t>0.9254,0.0298,0.0245,0.0013</t>
+  </si>
+  <si>
+    <t>0.9752,0.0209,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.7489,0.1260,0.0663,0.0024</t>
+  </si>
+  <si>
+    <t>0.5853,0.4315,0.0206,0.0029</t>
+  </si>
+  <si>
+    <t>0.9601,0.0183,0.0087,0.0036</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0011,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.6723,0.0044,0.3271,0.0011</t>
+  </si>
+  <si>
+    <t>0.0028,0.0005,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9924,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9968,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0154,0.9792,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.0708,0.0071,0.9219,0.0005</t>
+  </si>
+  <si>
+    <t>0.0147,0.0026,0.9797,0.0011</t>
+  </si>
+  <si>
+    <t>0.0181,0.2957,0.6651,0.0059</t>
+  </si>
+  <si>
+    <t>0.0117,0.0078,0.9775,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.0234,0.9941</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.7334,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9967,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.0189,0.9451,0.0804,0.0003</t>
+  </si>
+  <si>
+    <t>0.1359,0.7564,0.0892,0.0006</t>
+  </si>
+  <si>
+    <t>0.7126,0.1759,0.0622,0.0040</t>
+  </si>
+  <si>
+    <t>0.8647,0.0119,0.0212,0.0431</t>
+  </si>
+  <si>
+    <t>0.9728,0.0111,0.0045,0.0023</t>
+  </si>
+  <si>
+    <t>0.6190,0.0434,0.1952,0.0038</t>
+  </si>
+  <si>
+    <t>0.9341,0.0259,0.0132,0.0080</t>
+  </si>
+  <si>
+    <t>0.9451,0.0204,0.0174,0.0006</t>
+  </si>
+  <si>
+    <t>0.9115,0.0241,0.0267,0.0053</t>
+  </si>
+  <si>
+    <t>0.9792,0.0035,0.0060,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.9871,0.3347,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9020,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.2511,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1369,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.9097,0.0241,0.0131,0.0026</t>
+  </si>
+  <si>
+    <t>0.1181,0.0245,0.7926,0.0150</t>
+  </si>
+  <si>
+    <t>0.0012,0.0005,0.9975,0.0007</t>
+  </si>
+  <si>
+    <t>0.4798,0.0127,0.4995,0.0018</t>
+  </si>
+  <si>
+    <t>0.0036,0.0001,0.0016,0.9966</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0007,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0034,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.9913,0.9338,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0029,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.0089,0.9810,0.0081,0.0010</t>
+  </si>
+  <si>
+    <t>0.9711,0.0113,0.0052,0.0020</t>
+  </si>
+  <si>
+    <t>0.0088,0.9811,0.0107,0.0005</t>
+  </si>
+  <si>
+    <t>0.8616,0.0062,0.0590,0.0057</t>
+  </si>
+  <si>
+    <t>0.1622,0.0222,0.0008,0.8439</t>
+  </si>
+  <si>
+    <t>0.9951,0.0002,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0860,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.6032,0.0002,0.0732,0.0654</t>
+  </si>
+  <si>
+    <t>0.9002,0.0024,0.0503,0.0026</t>
+  </si>
+  <si>
+    <t>0.2644,0.7068,0.0316,0.0018</t>
+  </si>
+  <si>
+    <t>0.8784,0.0252,0.0356,0.0047</t>
+  </si>
+  <si>
+    <t>0.7159,0.0359,0.1567,0.0031</t>
+  </si>
+  <si>
+    <t>0.0540,0.8849,0.0432,0.0020</t>
+  </si>
+  <si>
+    <t>0.1760,0.0180,0.7872,0.0006</t>
+  </si>
+  <si>
+    <t>0.7195,0.1825,0.0427,0.0022</t>
+  </si>
+  <si>
+    <t>0.9452,0.0056,0.0188,0.0047</t>
+  </si>
+  <si>
+    <t>0.9805,0.0066,0.0035,0.0024</t>
+  </si>
+  <si>
+    <t>0.9303,0.0117,0.0281,0.0027</t>
+  </si>
+  <si>
+    <t>0.9397,0.0003,0.0054,0.0212</t>
+  </si>
+  <si>
+    <t>0.9154,0.0032,0.0343,0.0044</t>
+  </si>
+  <si>
+    <t>0.9221,0.0210,0.0260,0.0030</t>
+  </si>
+  <si>
+    <t>0.8785,0.0365,0.0420,0.0050</t>
+  </si>
+  <si>
+    <t>0.9777,0.0072,0.0050,0.0018</t>
+  </si>
+  <si>
+    <t>0.2278,0.8415,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0159,0.9422,0.0984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0288,0.9496,0.0296,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.1129,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0929,0.8894,0.0166,0.0013</t>
+  </si>
+  <si>
+    <t>0.7837,0.0999,0.0576,0.0021</t>
+  </si>
+  <si>
+    <t>0.4084,0.5729,0.0331,0.0018</t>
+  </si>
+  <si>
+    <t>0.2285,0.7286,0.0370,0.0034</t>
+  </si>
+  <si>
+    <t>0.0000,0.0295,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1526,0.1900,0.6979,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.1244,0.9886,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.0058,0.9945,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0233,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0021,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.0003,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0684,0.0074,0.9120,0.0025</t>
+  </si>
+  <si>
+    <t>0.0568,0.0040,0.9465,0.0003</t>
+  </si>
+  <si>
+    <t>0.0253,0.0989,0.8647,0.0028</t>
+  </si>
+  <si>
+    <t>0.2721,0.1761,0.3127,0.0009</t>
+  </si>
+  <si>
+    <t>0.0039,0.9735,0.0619,0.0071</t>
+  </si>
+  <si>
+    <t>0.0435,0.0028,0.9588,0.0001</t>
+  </si>
+  <si>
+    <t>0.6615,0.0611,0.0814,0.0133</t>
+  </si>
+  <si>
+    <t>0.0608,0.0150,0.9128,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.9932,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9968,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0049,0.9919,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0111,0.9855,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0074,0.9876,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.8766,0.0173,0.0484,0.0014</t>
+  </si>
+  <si>
+    <t>0.8732,0.0196,0.0539,0.0011</t>
+  </si>
+  <si>
+    <t>0.2844,0.0026,0.4939,0.0423</t>
+  </si>
+  <si>
+    <t>0.2449,0.0125,0.7284,0.0017</t>
+  </si>
+  <si>
+    <t>0.7877,0.0009,0.2686,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.1388,0.9866,0.0007</t>
+  </si>
+  <si>
+    <t>0.0081,0.1394,0.9533,0.0004</t>
+  </si>
+  <si>
+    <t>0.0071,0.0159,0.9834,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.2879,0.9750,0.0005</t>
+  </si>
+  <si>
+    <t>0.7896,0.2323,0.0115,0.0020</t>
+  </si>
+  <si>
+    <t>0.8840,0.1130,0.0122,0.0027</t>
+  </si>
+  <si>
+    <t>0.5663,0.4678,0.0183,0.0014</t>
+  </si>
+  <si>
+    <t>0.7919,0.1526,0.0396,0.0023</t>
+  </si>
+  <si>
+    <t>0.4055,0.5956,0.0242,0.0012</t>
+  </si>
+  <si>
+    <t>0.7885,0.1667,0.0318,0.0027</t>
+  </si>
+  <si>
+    <t>0.6181,0.2257,0.0827,0.0026</t>
+  </si>
+  <si>
+    <t>0.9790,0.0092,0.0038,0.0017</t>
+  </si>
+  <si>
+    <t>0.0008,0.0113,0.9978,0.0015</t>
+  </si>
+  <si>
+    <t>0.0108,0.2022,0.9022,0.0006</t>
+  </si>
+  <si>
+    <t>0.1032,0.0032,0.8569,0.0070</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9995,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0011,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0016,0.9957,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9203,0.0202,0.0223,0.0010</t>
-  </si>
-  <si>
-    <t>0.2321,0.0310,0.6588,0.0032</t>
-  </si>
-  <si>
-    <t>0.0762,0.8992,0.0238,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.9953,0.0095,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.6244,0.9737,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9992,0.0012</t>
-  </si>
-  <si>
-    <t>0.0003,0.1189,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.1265,0.0001,0.9100,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0730,0.9927,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.0101,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0214,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.0081,0.0111,0.9897</t>
-  </si>
-  <si>
-    <t>0.0002,0.9983,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0110,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0384,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3860,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0010,0.9961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.0003,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9990,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0014,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.9207,0.0845,0.0059,0.0013</t>
-  </si>
-  <si>
-    <t>0.6177,0.0187,0.2757,0.0022</t>
-  </si>
-  <si>
-    <t>0.9096,0.0990,0.0071,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.0501,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9519,0.0284,0.0079,0.0013</t>
-  </si>
-  <si>
-    <t>0.8483,0.0870,0.0302,0.0011</t>
-  </si>
-  <si>
-    <t>0.4639,0.4752,0.0494,0.0022</t>
-  </si>
-  <si>
-    <t>0.0000,0.9896,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0324,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0229,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9784,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9966,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2549,0.0033,0.7988,0.0004</t>
-  </si>
-  <si>
-    <t>0.0917,0.0322,0.8514,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0028,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.9550,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9849,0.9666,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.0765,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9766,0.9829,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.0001,0.5648,0.5661</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0046,0.9984</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0126,0.9973</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.7600,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9712,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9911,0.8967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9881,0.8905,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9931,0.9839,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.9741,0.0000</t>
-  </si>
-  <si>
-    <t>0.9682,0.0257,0.0045,0.0019</t>
-  </si>
-  <si>
-    <t>0.8227,0.1453,0.0302,0.0031</t>
-  </si>
-  <si>
-    <t>0.5384,0.5094,0.0124,0.0006</t>
-  </si>
-  <si>
-    <t>0.4914,0.4889,0.0256,0.0026</t>
-  </si>
-  <si>
-    <t>0.7830,0.2153,0.0141,0.0032</t>
-  </si>
-  <si>
-    <t>0.7807,0.1302,0.0467,0.0015</t>
-  </si>
-  <si>
-    <t>0.6324,0.2699,0.0575,0.0035</t>
-  </si>
-  <si>
-    <t>0.8609,0.1110,0.0229,0.0010</t>
-  </si>
-  <si>
-    <t>0.9656,0.0154,0.0084,0.0032</t>
-  </si>
-  <si>
-    <t>0.9033,0.0573,0.0253,0.0031</t>
-  </si>
-  <si>
-    <t>0.9601,0.0227,0.0078,0.0042</t>
-  </si>
-  <si>
-    <t>0.9400,0.0267,0.0167,0.0035</t>
-  </si>
-  <si>
-    <t>0.9731,0.0257,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.5742,0.3174,0.0606,0.0021</t>
-  </si>
-  <si>
-    <t>0.9542,0.0254,0.0089,0.0053</t>
-  </si>
-  <si>
-    <t>0.9893,0.0046,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0003,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.9476,0.0014,0.0375,0.0002</t>
-  </si>
-  <si>
-    <t>0.0068,0.0016,0.9896,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9904,0.0135,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.9957,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0191,0.9798,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0413,0.0419,0.8754,0.0073</t>
-  </si>
-  <si>
-    <t>0.0548,0.0047,0.9362,0.0022</t>
-  </si>
-  <si>
-    <t>0.2314,0.0187,0.6831,0.0043</t>
-  </si>
-  <si>
-    <t>0.0100,0.0140,0.9757,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0721,0.0036,0.9845</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0001,0.0050</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9952,0.9852,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9973,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.0488,0.9257,0.0276,0.0003</t>
-  </si>
-  <si>
-    <t>0.0150,0.9713,0.0173,0.0001</t>
-  </si>
-  <si>
-    <t>0.5510,0.2538,0.1440,0.0051</t>
-  </si>
-  <si>
-    <t>0.9461,0.0087,0.0095,0.0123</t>
-  </si>
-  <si>
-    <t>0.7570,0.0877,0.0854,0.0031</t>
-  </si>
-  <si>
-    <t>0.8245,0.0310,0.0666,0.0041</t>
-  </si>
-  <si>
-    <t>0.7647,0.1585,0.0463,0.0079</t>
-  </si>
-  <si>
-    <t>0.7784,0.0860,0.0702,0.0017</t>
-  </si>
-  <si>
-    <t>0.9179,0.0207,0.0278,0.0036</t>
-  </si>
-  <si>
-    <t>0.9409,0.0030,0.0124,0.0097</t>
-  </si>
-  <si>
-    <t>0.0000,0.9708,0.9897,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9798,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.2017,0.9851,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.0112,0.9904,0.0002</t>
-  </si>
-  <si>
-    <t>0.8772,0.0101,0.0752,0.0022</t>
-  </si>
-  <si>
-    <t>0.1626,0.0116,0.7954,0.0078</t>
-  </si>
-  <si>
-    <t>0.1414,0.0004,0.9007,0.0003</t>
-  </si>
-  <si>
-    <t>0.6200,0.0100,0.3323,0.0027</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.0007,0.9988</t>
+    <t>0.0000,0.9505,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.0007,0.9904,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0043,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0041,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0146,0.0057,0.9734,0.0022</t>
+  </si>
+  <si>
+    <t>0.5112,0.0016,0.5476,0.0012</t>
+  </si>
+  <si>
+    <t>0.7258,0.0003,0.3458,0.0005</t>
+  </si>
+  <si>
+    <t>0.9043,0.0016,0.0709,0.0015</t>
+  </si>
+  <si>
+    <t>0.1692,0.8006,0.0212,0.0019</t>
+  </si>
+  <si>
+    <t>0.7222,0.2286,0.0394,0.0050</t>
+  </si>
+  <si>
+    <t>0.8624,0.1420,0.0141,0.0022</t>
+  </si>
+  <si>
+    <t>0.8781,0.0939,0.0240,0.0037</t>
+  </si>
+  <si>
+    <t>0.8160,0.1546,0.0132,0.0130</t>
+  </si>
+  <si>
+    <t>0.5239,0.4027,0.0553,0.0014</t>
+  </si>
+  <si>
+    <t>0.2250,0.7827,0.0147,0.0007</t>
+  </si>
+  <si>
+    <t>0.8653,0.1230,0.0199,0.0022</t>
+  </si>
+  <si>
+    <t>0.0002,0.0382,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0571,0.9919,0.0007</t>
+  </si>
+  <si>
+    <t>0.0062,0.0460,0.9760,0.0005</t>
+  </si>
+  <si>
+    <t>0.0070,0.0005,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.1721,0.0003,0.7351,0.0110</t>
+  </si>
+  <si>
+    <t>0.0037,0.0012,0.9938,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.2074,0.0007,0.0052,0.8412</t>
+  </si>
+  <si>
+    <t>0.0008,0.0008,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0152,0.0002,0.0012,0.9923</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0000,0.0009,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0227,0.9971</t>
-  </si>
-  <si>
-    <t>0.0000,0.9889,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.9824,0.0046,0.0024,0.0022</t>
-  </si>
-  <si>
-    <t>0.0034,0.9908,0.0044,0.0008</t>
-  </si>
-  <si>
-    <t>0.9681,0.0064,0.0056,0.0041</t>
-  </si>
-  <si>
-    <t>0.0041,0.9889,0.0096,0.0003</t>
-  </si>
-  <si>
-    <t>0.4463,0.0085,0.4235,0.0088</t>
-  </si>
-  <si>
-    <t>0.1566,0.0300,0.0008,0.8348</t>
-  </si>
-  <si>
-    <t>0.9838,0.0014,0.0056,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.2644,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.6153,0.0008,0.0157,0.2200</t>
-  </si>
-  <si>
-    <t>0.8980,0.0042,0.0424,0.0026</t>
-  </si>
-  <si>
-    <t>0.0993,0.8631,0.0334,0.0012</t>
-  </si>
-  <si>
-    <t>0.7157,0.0948,0.0757,0.0086</t>
-  </si>
-  <si>
-    <t>0.8908,0.0190,0.0477,0.0011</t>
-  </si>
-  <si>
-    <t>0.0448,0.9253,0.0076,0.0088</t>
-  </si>
-  <si>
-    <t>0.5784,0.0230,0.3265,0.0006</t>
-  </si>
-  <si>
-    <t>0.8170,0.0173,0.1016,0.0008</t>
-  </si>
-  <si>
-    <t>0.9783,0.0027,0.0048,0.0041</t>
-  </si>
-  <si>
-    <t>0.9869,0.0029,0.0020,0.0026</t>
-  </si>
-  <si>
-    <t>0.8853,0.0212,0.0521,0.0025</t>
-  </si>
-  <si>
-    <t>0.8792,0.0051,0.0317,0.0236</t>
-  </si>
-  <si>
-    <t>0.7756,0.0519,0.0889,0.0061</t>
-  </si>
-  <si>
-    <t>0.8635,0.0961,0.0265,0.0031</t>
-  </si>
-  <si>
-    <t>0.9748,0.0033,0.0060,0.0025</t>
-  </si>
-  <si>
-    <t>0.9678,0.0083,0.0083,0.0030</t>
-  </si>
-  <si>
-    <t>0.2558,0.7460,0.0117,0.0009</t>
-  </si>
-  <si>
-    <t>0.0663,0.8434,0.1005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0269,0.9519,0.0274,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0862,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.2998,0.6472,0.0380,0.0020</t>
-  </si>
-  <si>
-    <t>0.7818,0.1329,0.0422,0.0014</t>
-  </si>
-  <si>
-    <t>0.5595,0.4552,0.0213,0.0022</t>
-  </si>
-  <si>
-    <t>0.0394,0.9280,0.0218,0.0034</t>
-  </si>
-  <si>
-    <t>0.0000,0.0408,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2828,0.0526,0.6267,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.2900,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0011,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.3244,0.9958,0.0002</t>
-  </si>
-  <si>
-    <t>0.0183,0.0010,0.9860,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0577,0.0041,0.9299,0.0015</t>
-  </si>
-  <si>
-    <t>0.0505,0.0009,0.9580,0.0004</t>
-  </si>
-  <si>
-    <t>0.7024,0.0148,0.2289,0.0007</t>
-  </si>
-  <si>
-    <t>0.0300,0.0858,0.8923,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.9843,0.0700,0.0054</t>
-  </si>
-  <si>
-    <t>0.0960,0.0098,0.8911,0.0003</t>
-  </si>
-  <si>
-    <t>0.0118,0.0084,0.9196,0.0509</t>
-  </si>
-  <si>
-    <t>0.0675,0.0492,0.8559,0.0018</t>
-  </si>
-  <si>
-    <t>0.0068,0.9888,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9986,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0138,0.9787,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.2483,0.8118,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.0204,0.9761,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.7394,0.1170,0.0307,0.0014</t>
-  </si>
-  <si>
-    <t>0.6805,0.0058,0.2962,0.0016</t>
-  </si>
-  <si>
-    <t>0.6886,0.0046,0.2076,0.0144</t>
-  </si>
-  <si>
-    <t>0.6193,0.0052,0.3936,0.0017</t>
-  </si>
-  <si>
-    <t>0.1785,0.0004,0.8490,0.0018</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.9965,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.2322,0.9929,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.1465,0.9922,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0128,0.9900,0.0004</t>
-  </si>
-  <si>
-    <t>0.0013,0.3034,0.9694,0.0007</t>
-  </si>
-  <si>
-    <t>0.9392,0.0620,0.0059,0.0017</t>
-  </si>
-  <si>
-    <t>0.7196,0.3184,0.0113,0.0019</t>
-  </si>
-  <si>
-    <t>0.8548,0.1510,0.0082,0.0037</t>
-  </si>
-  <si>
-    <t>0.9178,0.1002,0.0057,0.0011</t>
-  </si>
-  <si>
-    <t>0.7380,0.2749,0.0173,0.0023</t>
-  </si>
-  <si>
-    <t>0.9024,0.0739,0.0177,0.0018</t>
-  </si>
-  <si>
-    <t>0.7030,0.1284,0.0860,0.0037</t>
-  </si>
-  <si>
-    <t>0.9475,0.0376,0.0084,0.0045</t>
-  </si>
-  <si>
-    <t>0.0006,0.0071,0.9987,0.0008</t>
-  </si>
-  <si>
-    <t>0.0065,0.2159,0.9432,0.0005</t>
-  </si>
-  <si>
-    <t>0.0778,0.0017,0.5351,0.2282</t>
-  </si>
-  <si>
-    <t>0.0049,0.0001,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0037,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.7090,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0017,0.9964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0038,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0792,0.0051,0.8953,0.0058</t>
-  </si>
-  <si>
-    <t>0.7384,0.0058,0.2657,0.0010</t>
-  </si>
-  <si>
-    <t>0.1660,0.0044,0.8343,0.0041</t>
-  </si>
-  <si>
-    <t>0.8876,0.0008,0.0968,0.0013</t>
-  </si>
-  <si>
-    <t>0.1707,0.7913,0.0360,0.0017</t>
-  </si>
-  <si>
-    <t>0.7196,0.1179,0.1070,0.0069</t>
-  </si>
-  <si>
-    <t>0.7775,0.1567,0.0405,0.0016</t>
-  </si>
-  <si>
-    <t>0.5111,0.4947,0.0262,0.0013</t>
-  </si>
-  <si>
-    <t>0.6595,0.3368,0.0097,0.0058</t>
-  </si>
-  <si>
-    <t>0.7788,0.1923,0.0300,0.0017</t>
-  </si>
-  <si>
-    <t>0.1320,0.8700,0.0127,0.0004</t>
-  </si>
-  <si>
-    <t>0.8651,0.1326,0.0157,0.0028</t>
-  </si>
-  <si>
-    <t>0.0142,0.2007,0.8547,0.0035</t>
-  </si>
-  <si>
-    <t>0.0000,0.0109,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.5951,0.9744,0.0004</t>
-  </si>
-  <si>
-    <t>0.0180,0.0853,0.8938,0.0015</t>
-  </si>
-  <si>
-    <t>0.0014,0.0012,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0450,0.0004,0.7076,0.0939</t>
-  </si>
-  <si>
-    <t>0.0621,0.0045,0.9290,0.0018</t>
-  </si>
-  <si>
-    <t>0.0007,0.0022,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.6876,0.0011,0.0279,0.1091</t>
-  </si>
-  <si>
-    <t>0.0013,0.0007,0.0004,0.9990</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0003,1.0000</t>
-  </si>
-  <si>
-    <t>0.3211,0.0142,0.1541,0.1773</t>
+    <t>0.7536,0.0055,0.0361,0.0514</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1947,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1964,7 +1961,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1975,10 +1972,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1992,7 +1989,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2006,7 +2003,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2020,7 +2017,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2034,7 +2031,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2048,7 +2045,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2062,7 +2059,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2076,7 +2073,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2090,7 +2087,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2104,7 +2101,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2118,7 +2115,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2132,7 +2129,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2146,7 +2143,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2160,7 +2157,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2171,10 +2168,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2188,7 +2185,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2202,7 +2199,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2216,7 +2213,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2230,7 +2227,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2244,7 +2241,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2423,7 +2420,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
         <v>299</v>
@@ -2521,7 +2518,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>306</v>
@@ -2608,7 +2605,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2622,7 +2619,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2633,10 +2630,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2650,7 +2647,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2664,7 +2661,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2678,7 +2675,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2692,7 +2689,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2706,7 +2703,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2720,7 +2717,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2734,7 +2731,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2748,7 +2745,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2762,7 +2759,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2776,7 +2773,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2787,10 +2784,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2804,7 +2801,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2818,7 +2815,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2832,7 +2829,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2846,7 +2843,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2860,7 +2857,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2874,7 +2871,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2888,7 +2885,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2902,7 +2899,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,7 +2913,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2930,7 +2927,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2944,7 +2941,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,7 +2955,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2972,7 +2969,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2986,7 +2983,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2997,10 +2994,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3014,7 +3011,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3028,7 +3025,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3042,7 +3039,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3056,7 +3053,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3070,7 +3067,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3123,7 +3120,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
         <v>347</v>
@@ -3235,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D94" t="s">
         <v>355</v>
@@ -3823,7 +3820,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
         <v>397</v>
@@ -3921,7 +3918,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
         <v>404</v>
@@ -4201,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
         <v>424</v>
@@ -4425,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D179" t="s">
         <v>440</v>
@@ -4607,7 +4604,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>453</v>
@@ -4621,7 +4618,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
         <v>454</v>
@@ -4663,7 +4660,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
         <v>457</v>
@@ -4789,7 +4786,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
         <v>466</v>
@@ -4803,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>467</v>
@@ -4817,7 +4814,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
         <v>468</v>
@@ -4957,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D217" t="s">
         <v>478</v>
@@ -5167,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D232" t="s">
         <v>493</v>
@@ -5181,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
         <v>494</v>
@@ -5338,7 +5335,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>366</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5349,10 +5346,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5366,7 +5363,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5380,7 +5377,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,7 +5391,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5408,7 +5405,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5422,7 +5419,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5433,10 +5430,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5450,7 +5447,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5464,7 +5461,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5478,7 +5475,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>406</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5492,7 +5489,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>406</v>
+        <v>514</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5506,7 +5503,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
